--- a/template/horaire.xlsx
+++ b/template/horaire.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/etiennerivard/notes_de_cours/techinfo/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1528A92C-C8A2-614D-9AF6-75049B7C42DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349B6EAB-B5E6-2E46-94E1-B8B37182A47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="700" windowWidth="28580" windowHeight="17780" xr2:uid="{6B795B45-6C14-B04F-B93D-A59A5BE3A68D}"/>
+    <workbookView xWindow="0" yWindow="700" windowWidth="16960" windowHeight="17780" xr2:uid="{6B795B45-6C14-B04F-B93D-A59A5BE3A68D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="82">
   <si>
     <t>Lundi</t>
   </si>
@@ -249,49 +249,40 @@
     <t>14:05</t>
   </si>
   <si>
-    <t>ST</t>
-  </si>
-  <si>
-    <t>Conception de systèmes </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Développement Web 1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Réseautique </t>
-  </si>
-  <si>
-    <t>Simulations en astrophysique</t>
-  </si>
-  <si>
-    <t>C309</t>
-  </si>
-  <si>
-    <t>E210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Création multimédia </t>
-  </si>
-  <si>
-    <t>ES12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Objets connectés 2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mégadonnées </t>
-  </si>
-  <si>
-    <t>Virgil</t>
-  </si>
-  <si>
-    <t>VD</t>
-  </si>
-  <si>
-    <t>E205</t>
-  </si>
-  <si>
-    <t>E304</t>
+    <t>Bases de données 2</t>
+  </si>
+  <si>
+    <t>Dévelopment Web 3</t>
+  </si>
+  <si>
+    <t>Piratage éthique</t>
+  </si>
+  <si>
+    <t>Design Web</t>
+  </si>
+  <si>
+    <t>Technologies émergentes</t>
+  </si>
+  <si>
+    <t>Jeux 3D</t>
+  </si>
+  <si>
+    <t>C210</t>
+  </si>
+  <si>
+    <t>Intelligences artificielles</t>
+  </si>
+  <si>
+    <t>CR09</t>
+  </si>
+  <si>
+    <t>Projet intégrateur 1</t>
+  </si>
+  <si>
+    <t>Programmation 1</t>
+  </si>
+  <si>
+    <t>Jeux 2D</t>
   </si>
 </sst>
 </file>
@@ -342,12 +333,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -376,11 +368,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{29040E5A-5519-964C-B6DE-2A568682510C}" name="Table1" displayName="Table1" ref="A1:I29" totalsRowShown="0">
-  <autoFilter ref="A1:I29" xr:uid="{29040E5A-5519-964C-B6DE-2A568682510C}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I29">
-    <sortCondition ref="E2:E29"/>
-    <sortCondition ref="A2:A29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{29040E5A-5519-964C-B6DE-2A568682510C}" name="Table1" displayName="Table1" ref="A1:I23" totalsRowShown="0">
+  <autoFilter ref="A1:I23" xr:uid="{29040E5A-5519-964C-B6DE-2A568682510C}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I23">
+    <sortCondition ref="E2:E23"/>
+    <sortCondition ref="A2:A23"/>
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{886CAE80-8B7C-814A-A2B4-5713C370F8E6}" name="day"/>
@@ -714,7 +706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46DF1DC5-63E0-A14F-8B6A-86AB73F394B2}">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -753,25 +745,25 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D2" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G2" t="s">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="H2" t="s">
         <v>56</v>
@@ -782,25 +774,25 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D3" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H3" t="s">
         <v>56</v>
@@ -811,25 +803,25 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G4" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="H4" t="s">
         <v>56</v>
@@ -843,22 +835,22 @@
         <v>20</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D5" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H5" t="s">
         <v>56</v>
@@ -869,28 +861,28 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D6" s="2">
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H6" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -901,25 +893,25 @@
         <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D7" s="2">
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G7" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -927,28 +919,28 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D8" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="G8" t="s">
         <v>7</v>
       </c>
       <c r="H8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -956,28 +948,28 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="4" t="s">
         <v>43</v>
       </c>
       <c r="D9" s="2">
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="F9" t="s">
         <v>72</v>
       </c>
       <c r="G9" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -985,13 +977,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D10" s="2">
         <v>2</v>
@@ -1000,10 +992,10 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="G10" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H10" t="s">
         <v>33</v>
@@ -1014,13 +1006,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D11" s="2">
         <v>2</v>
@@ -1029,10 +1021,10 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="G11" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H11" t="s">
         <v>33</v>
@@ -1045,11 +1037,11 @@
       <c r="A12" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>44</v>
+      <c r="B12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="D12" s="2">
         <v>2</v>
@@ -1058,10 +1050,10 @@
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="G12" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H12" t="s">
         <v>33</v>
@@ -1072,28 +1064,28 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D13" s="2">
         <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="G13" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="H13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -1104,170 +1096,170 @@
         <v>0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D14" s="2">
         <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s">
         <v>73</v>
       </c>
       <c r="G14" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D15" s="2">
         <v>3</v>
       </c>
       <c r="E15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F15" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="G15" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="H15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>45</v>
+        <v>3</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="D16" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="G16" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="H16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I16">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>43</v>
       </c>
       <c r="D17" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F17" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="G17" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="H17" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I17">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="D18" s="2">
         <v>2</v>
       </c>
       <c r="E18" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F18" t="s">
         <v>73</v>
       </c>
       <c r="G18" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H18" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D19" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="F19" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="G19" t="s">
         <v>7</v>
       </c>
       <c r="H19" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="I19">
         <v>1</v>
@@ -1275,13 +1267,13 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D20" s="2">
         <v>2</v>
@@ -1290,10 +1282,10 @@
         <v>67</v>
       </c>
       <c r="F20" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="H20" t="s">
         <v>37</v>
@@ -1304,25 +1296,25 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D21" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21" t="s">
         <v>67</v>
       </c>
       <c r="F21" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H21" t="s">
         <v>37</v>
@@ -1333,28 +1325,28 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D22" s="2">
         <v>2</v>
       </c>
       <c r="E22" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F22" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s">
-        <v>84</v>
+        <v>2</v>
       </c>
       <c r="H22" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="I22">
         <v>1</v>
@@ -1362,291 +1354,30 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D23" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="F23" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="G23" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="H23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="2">
-        <v>2</v>
-      </c>
-      <c r="E24" t="s">
-        <v>29</v>
-      </c>
-      <c r="F24" t="s">
-        <v>53</v>
-      </c>
-      <c r="G24" t="s">
-        <v>21</v>
-      </c>
-      <c r="H24" t="s">
-        <v>39</v>
-      </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D25" s="2">
-        <v>3</v>
-      </c>
-      <c r="E25" t="s">
-        <v>81</v>
-      </c>
-      <c r="F25" t="s">
-        <v>71</v>
-      </c>
-      <c r="G25" t="s">
-        <v>83</v>
-      </c>
-      <c r="H25" t="s">
-        <v>82</v>
-      </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="2">
-        <v>3</v>
-      </c>
-      <c r="E26" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" t="s">
-        <v>60</v>
-      </c>
-      <c r="G26" t="s">
-        <v>2</v>
-      </c>
-      <c r="H26" t="s">
-        <v>70</v>
-      </c>
-      <c r="I26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D27" s="2">
-        <v>3</v>
-      </c>
-      <c r="E27" t="s">
-        <v>27</v>
-      </c>
-      <c r="F27" t="s">
-        <v>64</v>
-      </c>
-      <c r="G27" t="s">
-        <v>2</v>
-      </c>
-      <c r="H27" t="s">
-        <v>70</v>
-      </c>
-      <c r="I27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>20</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D28" s="2">
-        <v>3</v>
-      </c>
-      <c r="E28" t="s">
-        <v>27</v>
-      </c>
-      <c r="F28" t="s">
-        <v>64</v>
-      </c>
-      <c r="G28" t="s">
-        <v>2</v>
-      </c>
-      <c r="H28" t="s">
-        <v>70</v>
-      </c>
-      <c r="I28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>20</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D29" s="2">
-        <v>3</v>
-      </c>
-      <c r="E29" t="s">
-        <v>27</v>
-      </c>
-      <c r="F29" t="s">
-        <v>60</v>
-      </c>
-      <c r="G29" t="s">
-        <v>2</v>
-      </c>
-      <c r="H29" t="s">
-        <v>70</v>
-      </c>
-      <c r="I29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="2">
-        <v>3</v>
-      </c>
-      <c r="E30" t="s">
-        <v>29</v>
-      </c>
-      <c r="F30" t="s">
-        <v>79</v>
-      </c>
-      <c r="G30" t="s">
-        <v>7</v>
-      </c>
-      <c r="H30" t="s">
-        <v>39</v>
-      </c>
-      <c r="I30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>19</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D31" s="2">
-        <v>2</v>
-      </c>
-      <c r="E31" t="s">
-        <v>29</v>
-      </c>
-      <c r="F31" t="s">
-        <v>80</v>
-      </c>
-      <c r="G31" t="s">
-        <v>7</v>
-      </c>
-      <c r="H31" t="s">
-        <v>39</v>
-      </c>
-      <c r="I31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>20</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" s="2">
-        <v>2</v>
-      </c>
-      <c r="E32" t="s">
-        <v>29</v>
-      </c>
-      <c r="F32" t="s">
-        <v>80</v>
-      </c>
-      <c r="G32" t="s">
-        <v>7</v>
-      </c>
-      <c r="H32" t="s">
-        <v>39</v>
-      </c>
-      <c r="I32">
         <v>1</v>
       </c>
     </row>

--- a/template/horaire.xlsx
+++ b/template/horaire.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/etiennerivard/notes_de_cours/techinfo/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349B6EAB-B5E6-2E46-94E1-B8B37182A47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338FE1D7-6DA8-6040-8607-E532F9F5F660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="16960" windowHeight="17780" xr2:uid="{6B795B45-6C14-B04F-B93D-A59A5BE3A68D}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="83">
   <si>
     <t>Lundi</t>
   </si>
@@ -283,6 +283,9 @@
   </si>
   <si>
     <t>Jeux 2D</t>
+  </si>
+  <si>
+    <t>Objets connectés 1</t>
   </si>
 </sst>
 </file>
@@ -368,8 +371,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{29040E5A-5519-964C-B6DE-2A568682510C}" name="Table1" displayName="Table1" ref="A1:I23" totalsRowShown="0">
-  <autoFilter ref="A1:I23" xr:uid="{29040E5A-5519-964C-B6DE-2A568682510C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{29040E5A-5519-964C-B6DE-2A568682510C}" name="Table1" displayName="Table1" ref="A1:I30" totalsRowShown="0">
+  <autoFilter ref="A1:I30" xr:uid="{29040E5A-5519-964C-B6DE-2A568682510C}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I23">
     <sortCondition ref="E2:E23"/>
     <sortCondition ref="A2:A23"/>
@@ -706,7 +709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46DF1DC5-63E0-A14F-8B6A-86AB73F394B2}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -1379,6 +1382,209 @@
       </c>
       <c r="I23">
         <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="2">
+        <v>2</v>
+      </c>
+      <c r="E24" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" t="s">
+        <v>80</v>
+      </c>
+      <c r="G24" t="s">
+        <v>2</v>
+      </c>
+      <c r="H24" t="s">
+        <v>39</v>
+      </c>
+      <c r="I24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="2">
+        <v>2</v>
+      </c>
+      <c r="E25" t="s">
+        <v>29</v>
+      </c>
+      <c r="F25" t="s">
+        <v>82</v>
+      </c>
+      <c r="G25" t="s">
+        <v>7</v>
+      </c>
+      <c r="H25" t="s">
+        <v>39</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="2">
+        <v>2</v>
+      </c>
+      <c r="E26" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26" t="s">
+        <v>54</v>
+      </c>
+      <c r="G26" t="s">
+        <v>7</v>
+      </c>
+      <c r="H26" t="s">
+        <v>39</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" s="2">
+        <v>2</v>
+      </c>
+      <c r="E27" t="s">
+        <v>29</v>
+      </c>
+      <c r="F27" t="s">
+        <v>80</v>
+      </c>
+      <c r="G27" t="s">
+        <v>2</v>
+      </c>
+      <c r="H27" t="s">
+        <v>39</v>
+      </c>
+      <c r="I27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28" s="2">
+        <v>2</v>
+      </c>
+      <c r="E28" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" t="s">
+        <v>7</v>
+      </c>
+      <c r="H28" t="s">
+        <v>39</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="2">
+        <v>2</v>
+      </c>
+      <c r="E29" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29" t="s">
+        <v>54</v>
+      </c>
+      <c r="G29" t="s">
+        <v>7</v>
+      </c>
+      <c r="H29" t="s">
+        <v>39</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" s="2">
+        <v>2</v>
+      </c>
+      <c r="E30" t="s">
+        <v>29</v>
+      </c>
+      <c r="F30" t="s">
+        <v>80</v>
+      </c>
+      <c r="G30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H30" t="s">
+        <v>39</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/template/horaire.xlsx
+++ b/template/horaire.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/etiennerivard/notes_de_cours/techinfo/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338FE1D7-6DA8-6040-8607-E532F9F5F660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA6E249-5DA8-C141-B1C2-481C16763334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="16960" windowHeight="17780" xr2:uid="{6B795B45-6C14-B04F-B93D-A59A5BE3A68D}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="86">
   <si>
     <t>Lundi</t>
   </si>
@@ -286,6 +286,15 @@
   </si>
   <si>
     <t>Objets connectés 1</t>
+  </si>
+  <si>
+    <t>Outils informatique</t>
+  </si>
+  <si>
+    <t>Gestion d'un poste informatique</t>
+  </si>
+  <si>
+    <t>Dévelopment Web 2</t>
   </si>
 </sst>
 </file>
@@ -371,8 +380,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{29040E5A-5519-964C-B6DE-2A568682510C}" name="Table1" displayName="Table1" ref="A1:I30" totalsRowShown="0">
-  <autoFilter ref="A1:I30" xr:uid="{29040E5A-5519-964C-B6DE-2A568682510C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{29040E5A-5519-964C-B6DE-2A568682510C}" name="Table1" displayName="Table1" ref="A1:I38" totalsRowShown="0">
+  <autoFilter ref="A1:I38" xr:uid="{29040E5A-5519-964C-B6DE-2A568682510C}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I23">
     <sortCondition ref="E2:E23"/>
     <sortCondition ref="A2:A23"/>
@@ -709,7 +718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46DF1DC5-63E0-A14F-8B6A-86AB73F394B2}">
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -1585,6 +1594,238 @@
       </c>
       <c r="I30">
         <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" s="2">
+        <v>2</v>
+      </c>
+      <c r="E31" t="s">
+        <v>26</v>
+      </c>
+      <c r="F31" t="s">
+        <v>83</v>
+      </c>
+      <c r="G31" t="s">
+        <v>6</v>
+      </c>
+      <c r="H31" t="s">
+        <v>36</v>
+      </c>
+      <c r="I31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" s="2">
+        <v>2</v>
+      </c>
+      <c r="E32" t="s">
+        <v>26</v>
+      </c>
+      <c r="F32" t="s">
+        <v>83</v>
+      </c>
+      <c r="G32" t="s">
+        <v>6</v>
+      </c>
+      <c r="H32" t="s">
+        <v>36</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>19</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33" s="2">
+        <v>3</v>
+      </c>
+      <c r="E33" t="s">
+        <v>26</v>
+      </c>
+      <c r="F33" t="s">
+        <v>84</v>
+      </c>
+      <c r="G33" t="s">
+        <v>2</v>
+      </c>
+      <c r="H33" t="s">
+        <v>36</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" s="2">
+        <v>2</v>
+      </c>
+      <c r="E34" t="s">
+        <v>26</v>
+      </c>
+      <c r="F34" t="s">
+        <v>85</v>
+      </c>
+      <c r="G34" t="s">
+        <v>21</v>
+      </c>
+      <c r="H34" t="s">
+        <v>36</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D35" s="2">
+        <v>1</v>
+      </c>
+      <c r="E35" t="s">
+        <v>26</v>
+      </c>
+      <c r="F35" t="s">
+        <v>85</v>
+      </c>
+      <c r="G35" t="s">
+        <v>7</v>
+      </c>
+      <c r="H35" t="s">
+        <v>36</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" s="2">
+        <v>2</v>
+      </c>
+      <c r="E36" t="s">
+        <v>26</v>
+      </c>
+      <c r="F36" t="s">
+        <v>85</v>
+      </c>
+      <c r="G36" t="s">
+        <v>2</v>
+      </c>
+      <c r="H36" t="s">
+        <v>36</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" s="2">
+        <v>2</v>
+      </c>
+      <c r="E37" t="s">
+        <v>26</v>
+      </c>
+      <c r="F37" t="s">
+        <v>83</v>
+      </c>
+      <c r="G37" t="s">
+        <v>76</v>
+      </c>
+      <c r="H37" t="s">
+        <v>36</v>
+      </c>
+      <c r="I37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38" s="2">
+        <v>2</v>
+      </c>
+      <c r="E38" t="s">
+        <v>26</v>
+      </c>
+      <c r="F38" t="s">
+        <v>83</v>
+      </c>
+      <c r="G38" t="s">
+        <v>76</v>
+      </c>
+      <c r="H38" t="s">
+        <v>36</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/template/horaire.xlsx
+++ b/template/horaire.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/etiennerivard/notes_de_cours/techinfo/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA6E249-5DA8-C141-B1C2-481C16763334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D147A097-15A3-9F40-8115-C0A8202C1448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="16960" windowHeight="17780" xr2:uid="{6B795B45-6C14-B04F-B93D-A59A5BE3A68D}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="92">
   <si>
     <t>Lundi</t>
   </si>
@@ -295,6 +295,24 @@
   </si>
   <si>
     <t>Dévelopment Web 2</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>Analyse de données en gestion</t>
+  </si>
+  <si>
+    <t>Fonctionnement de l'ordinateur</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Nano-ordinateurs</t>
+  </si>
+  <si>
+    <t>B121</t>
   </si>
 </sst>
 </file>
@@ -351,7 +369,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -380,8 +398,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{29040E5A-5519-964C-B6DE-2A568682510C}" name="Table1" displayName="Table1" ref="A1:I38" totalsRowShown="0">
-  <autoFilter ref="A1:I38" xr:uid="{29040E5A-5519-964C-B6DE-2A568682510C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{29040E5A-5519-964C-B6DE-2A568682510C}" name="Table1" displayName="Table1" ref="A1:I49" totalsRowShown="0">
+  <autoFilter ref="A1:I49" xr:uid="{29040E5A-5519-964C-B6DE-2A568682510C}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I23">
     <sortCondition ref="E2:E23"/>
     <sortCondition ref="A2:A23"/>
@@ -718,7 +736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46DF1DC5-63E0-A14F-8B6A-86AB73F394B2}">
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -1165,10 +1183,10 @@
       <c r="A16" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D16" s="2">
@@ -1194,10 +1212,10 @@
       <c r="A17" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D17" s="2">
@@ -1426,10 +1444,10 @@
       <c r="A25" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D25" s="2">
@@ -1484,10 +1502,10 @@
       <c r="A27" t="s">
         <v>3</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D27" s="2">
@@ -1513,10 +1531,10 @@
       <c r="A28" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D28" s="2">
@@ -1542,10 +1560,10 @@
       <c r="A29" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D29" s="2">
@@ -1600,10 +1618,10 @@
       <c r="A31" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D31" s="2">
@@ -1629,10 +1647,10 @@
       <c r="A32" t="s">
         <v>0</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D32" s="2">
@@ -1687,10 +1705,10 @@
       <c r="A34" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D34" s="2">
@@ -1774,10 +1792,10 @@
       <c r="A37" t="s">
         <v>20</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D37" s="2">
@@ -1803,10 +1821,10 @@
       <c r="A38" t="s">
         <v>20</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D38" s="2">
@@ -1826,6 +1844,325 @@
       </c>
       <c r="I38">
         <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" s="2">
+        <v>2</v>
+      </c>
+      <c r="E39" t="s">
+        <v>27</v>
+      </c>
+      <c r="F39" t="s">
+        <v>87</v>
+      </c>
+      <c r="G39" t="s">
+        <v>21</v>
+      </c>
+      <c r="H39" t="s">
+        <v>86</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" s="2">
+        <v>2</v>
+      </c>
+      <c r="E40" t="s">
+        <v>27</v>
+      </c>
+      <c r="F40" t="s">
+        <v>87</v>
+      </c>
+      <c r="G40" t="s">
+        <v>21</v>
+      </c>
+      <c r="H40" t="s">
+        <v>86</v>
+      </c>
+      <c r="I40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>19</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41" s="2">
+        <v>2</v>
+      </c>
+      <c r="E41" t="s">
+        <v>27</v>
+      </c>
+      <c r="F41" t="s">
+        <v>88</v>
+      </c>
+      <c r="G41" t="s">
+        <v>2</v>
+      </c>
+      <c r="H41" t="s">
+        <v>86</v>
+      </c>
+      <c r="I41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42" s="2">
+        <v>2</v>
+      </c>
+      <c r="E42" t="s">
+        <v>27</v>
+      </c>
+      <c r="F42" t="s">
+        <v>88</v>
+      </c>
+      <c r="G42" t="s">
+        <v>2</v>
+      </c>
+      <c r="H42" t="s">
+        <v>86</v>
+      </c>
+      <c r="I42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>20</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D43" s="2">
+        <v>2</v>
+      </c>
+      <c r="E43" t="s">
+        <v>27</v>
+      </c>
+      <c r="F43" t="s">
+        <v>88</v>
+      </c>
+      <c r="G43" t="s">
+        <v>2</v>
+      </c>
+      <c r="H43" t="s">
+        <v>86</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>20</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D44" s="2">
+        <v>2</v>
+      </c>
+      <c r="E44" t="s">
+        <v>27</v>
+      </c>
+      <c r="F44" t="s">
+        <v>88</v>
+      </c>
+      <c r="G44" t="s">
+        <v>2</v>
+      </c>
+      <c r="H44" t="s">
+        <v>86</v>
+      </c>
+      <c r="I44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D45" s="2">
+        <v>2</v>
+      </c>
+      <c r="E45" t="s">
+        <v>27</v>
+      </c>
+      <c r="F45" t="s">
+        <v>87</v>
+      </c>
+      <c r="G45" t="s">
+        <v>21</v>
+      </c>
+      <c r="H45" t="s">
+        <v>86</v>
+      </c>
+      <c r="I45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D46" s="2">
+        <v>2</v>
+      </c>
+      <c r="E46" t="s">
+        <v>27</v>
+      </c>
+      <c r="F46" t="s">
+        <v>87</v>
+      </c>
+      <c r="G46" t="s">
+        <v>2</v>
+      </c>
+      <c r="H46" t="s">
+        <v>86</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>0</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D47" s="2">
+        <v>2</v>
+      </c>
+      <c r="E47" t="s">
+        <v>89</v>
+      </c>
+      <c r="F47" t="s">
+        <v>87</v>
+      </c>
+      <c r="G47" t="s">
+        <v>91</v>
+      </c>
+      <c r="H47" t="s">
+        <v>89</v>
+      </c>
+      <c r="I47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D48" s="2">
+        <v>3</v>
+      </c>
+      <c r="E48" t="s">
+        <v>89</v>
+      </c>
+      <c r="F48" t="s">
+        <v>90</v>
+      </c>
+      <c r="G48" t="s">
+        <v>2</v>
+      </c>
+      <c r="H48" t="s">
+        <v>89</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>19</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D49" s="2">
+        <v>2</v>
+      </c>
+      <c r="E49" t="s">
+        <v>89</v>
+      </c>
+      <c r="F49" t="s">
+        <v>87</v>
+      </c>
+      <c r="G49" t="s">
+        <v>21</v>
+      </c>
+      <c r="H49" t="s">
+        <v>89</v>
+      </c>
+      <c r="I49">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
